--- a/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MAR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60FFF4CF-574B-41A5-A749-02B08CD6995F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3C52D70-A22A-4974-B9A3-C2516490260D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -615,10 +615,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>WaD,WaP,SaD,RaP,FaD,FaP,SaP,RaD</t>
-  </si>
-  <si>
-    <t>RaN,SaN,WaN,FaP,SaP,RaP,FaN,WaP</t>
+    <t>FaD,RaP,WaP,RaD,WaD,SaD,FaP,SaP</t>
+  </si>
+  <si>
+    <t>RaP,SaN,WaN,RaN,FaP,SaP,WaP,FaN</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>RaN,SaN,WaN,FaP,SaP,RaP,FaN,WaP</v>
+        <v>RaP,SaN,WaN,RaN,FaP,SaP,WaP,FaN</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>WaD,WaP,SaD,RaP,FaD,FaP,SaP,RaD</v>
+        <v>FaD,RaP,WaP,RaD,WaD,SaD,FaP,SaP</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1341,7 +1341,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D99A655-73A2-43A2-9789-D63E631D6BD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70328ACA-D876-4C6D-A728-7B85B00C6B3C}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1425,7 +1425,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E49F51-C386-44A2-BA69-523CE19D282F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE6EFF2C-BBB9-4615-ACB2-25766F76772C}">
   <dimension ref="B9:O298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10271,7 +10271,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94775D8E-8FB8-41EA-A03F-437F6718618C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59045987-DD2C-4C9A-8565-FB2A57A81331}">
   <dimension ref="B9:BL67"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16149,7 +16149,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CC2A6F-AD7C-4633-A690-2897E4F21855}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C67AA2-4D20-45A5-B07F-184B6FF0C0AD}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16347,7 +16347,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECE34E72-6F3E-4544-912E-AAFED7B8F0F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472593D0-C2EC-430C-A7ED-3DAD23C8DE12}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16638,7 +16638,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE154D11-CDA5-4B6F-8B1E-53A5CD7F29BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D098855-1CCD-4E30-A780-B1F87FB3F601}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16797,7 +16797,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B96175D-B00B-41EE-9E56-E9C0D50364BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EEDBA3F-9915-4821-B328-9AA7AC367B64}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16955,7 +16955,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>7.6133333333333345E-2</v>
+        <v>7.6133333333333331E-2</v>
       </c>
       <c r="E20" t="s">
         <v>198</v>
@@ -17221,7 +17221,7 @@
         <v>37</v>
       </c>
       <c r="D39">
-        <v>0.11346666666666667</v>
+        <v>0.11346666666666666</v>
       </c>
       <c r="E39" t="s">
         <v>198</v>
@@ -17277,7 +17277,7 @@
         <v>37</v>
       </c>
       <c r="D43">
-        <v>9.3833333333333338E-2</v>
+        <v>9.3833333333333324E-2</v>
       </c>
       <c r="E43" t="s">
         <v>198</v>
@@ -17347,7 +17347,7 @@
         <v>41</v>
       </c>
       <c r="D48">
-        <v>0.20243333333333335</v>
+        <v>0.20243333333333333</v>
       </c>
       <c r="E48" t="s">
         <v>198</v>
@@ -17445,7 +17445,7 @@
         <v>37</v>
       </c>
       <c r="D55">
-        <v>0.14709999999999998</v>
+        <v>0.14710000000000001</v>
       </c>
       <c r="E55" t="s">
         <v>198</v>
@@ -17683,7 +17683,7 @@
         <v>41</v>
       </c>
       <c r="D72">
-        <v>0.15516666666666667</v>
+        <v>0.15516666666666665</v>
       </c>
       <c r="E72" t="s">
         <v>198</v>
@@ -17725,7 +17725,7 @@
         <v>37</v>
       </c>
       <c r="D75">
-        <v>0.17656666666666668</v>
+        <v>0.17656666666666665</v>
       </c>
       <c r="E75" t="s">
         <v>198</v>
@@ -17907,7 +17907,7 @@
         <v>41</v>
       </c>
       <c r="D88">
-        <v>0.12173333333333335</v>
+        <v>0.12173333333333332</v>
       </c>
       <c r="E88" t="s">
         <v>198</v>
@@ -18005,7 +18005,7 @@
         <v>37</v>
       </c>
       <c r="D95">
-        <v>0.13753333333333331</v>
+        <v>0.13753333333333334</v>
       </c>
       <c r="E95" t="s">
         <v>198</v>
@@ -18131,7 +18131,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.18330000000000002</v>
+        <v>0.18329999999999999</v>
       </c>
       <c r="E104" t="s">
         <v>198</v>
@@ -18341,7 +18341,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.18910000000000002</v>
+        <v>0.18909999999999996</v>
       </c>
       <c r="E119" t="s">
         <v>198</v>
@@ -18411,7 +18411,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.18566666666666667</v>
+        <v>0.18566666666666665</v>
       </c>
       <c r="E124" t="s">
         <v>198</v>
